--- a/daily_matches/job_matches_2026-08-16.xlsx
+++ b/daily_matches/job_matches_2026-08-16.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Engineer - AI Gateway</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cinter Networks</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>23.3</v>
+        <v>16.7</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, Redshift, BigQuery, Synapse, Docker, CI/CD, GitHub Actions, Terraform</t>
+          <t>RAG, FastAPI, Docker, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, Kafka</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0d5d92a233a5130</t>
+          <t>https://www.indeed.com/viewjob?jk=dfe651047abaadcf</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Disney Experiences</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Glue, Redshift, Kinesis, CI/CD, Git, Snowflake, Redshift</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37b325f2f84b39b8</t>
+          <t>https://www.indeed.com/viewjob?jk=37b50b0aef4d49b0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power BI Engineer</t>
+          <t>Sr. Associate Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Synapse, CI/CD, Git, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Kafka, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,59 +566,59 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8dfc6ba885136236</t>
+          <t>https://www.indeed.com/viewjob?jk=ccc557eea54e41a1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>GenAI Data Scientist, Commercial, Supply Chain &amp; Trading</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Colas USA</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Spring, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Synapse, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e57d8b4886da861</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2254a5e54551fb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer, Databricks</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Colas</t>
+          <t>Pearson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Englewood, CO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Synapse, CI/CD, GitHub Actions, Terraform, Git, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>EC2, BigQuery, Kinesis, Terraform, Git, BigQuery, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=623e6ba410872463</t>
+          <t>https://www.indeed.com/viewjob?jk=13516b225489ef52</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Java Engineer</t>
+          <t>Senior AI/ML Platform Engineer, GovCloud</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Medallia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>TensorFlow, S3, EC2, Kubernetes, Kafka, Hadoop, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=555e28a50da34fa7</t>
+          <t>https://www.indeed.com/viewjob?jk=8a5f83cd6892d049</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Ruby Developer</t>
+          <t>Senior Engineer, IT Data</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, Git, PostgreSQL, MySQL, SQL, R, Java, Scala</t>
+          <t>RAG, Data Lake, CI/CD, Jenkins, Terraform, Git, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,182 +706,77 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5cb901d6c7646a7</t>
+          <t>https://www.indeed.com/viewjob?jk=ca4c7fcf944f91e0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>AI Software Engineer Intern</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, NoSQL, Power BI, SQL, R, Java, Scala, Optimization</t>
+          <t>LangChain, Hugging Face, Pinecone, TensorFlow, PyTorch, FastAPI, Git, Snowflake, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d76837dc53c3d4</t>
+          <t>https://www.indeed.com/viewjob?jk=918ca0e4dac90e8e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Statistical Modeling &amp; Global Conflict Foresight Fellow International Truth &amp; Trauma Institute</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>infinite choice</t>
+          <t>Tailored Health LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, NoSQL, Power BI, SQL, R, Java, Scala, Optimization</t>
+          <t>RAG, TensorFlow, PyTorch, Git, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f269718b207b8002</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>infinite choice</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, NoSQL, Power BI, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=53d3f9868177e79c</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Software Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>infinite choice</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, NoSQL, Power BI, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bd4b1981eaabef6</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Software Engineer Senior-Ai Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>PNC Financial Services Group</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-08-15</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c6c4157e6b7880ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fd7b3192805f603f</t>
         </is>
       </c>
     </row>
